--- a/tame_output/ON/bt/strategyON_20240327.xlsx
+++ b/tame_output/ON/bt/strategyON_20240327.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-400.0%</t>
+          <t>-400.1%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-163.7%</t>
+          <t>-163.8%</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-144.1%</t>
+          <t>-144.3%</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-90.2%</t>
+          <t>-90.3%</t>
         </is>
       </c>
     </row>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74769908470241</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096474</v>
+        <v>3.856158176096472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.69292828007764</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879199</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568103</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963415</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192813</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.486558612509473</v>
+        <v>3.486558612509469</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-2.383799644201614</v>
+        <v>-2.385611703600269</v>
       </c>
       <c r="E1915" t="n">
-        <v>2.124943458957468</v>
+        <v>2.124218635198006</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.7991481325332578</v>
+        <v>0.7973360731346035</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.558308620471816</v>
+        <v>3.557221384832623</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240327.xlsx
+++ b/tame_output/ON/bt/strategyON_20240327.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>26.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-67.1%</t>
+          <t>-69.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.9%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.3%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-539.9%</t>
+          <t>-571.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-44.3%</t>
+          <t>-45.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-61.4%</t>
+          <t>-64.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>499.6%</t>
+          <t>908.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-400.1%</t>
+          <t>-431.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-216.3%</t>
+          <t>-228.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-35.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-62.6%</t>
+          <t>-50.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-218.8%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-163.8%</t>
+          <t>-176.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-281.3%</t>
+          <t>-312.4%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-148.2%</t>
+          <t>-160.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-144.3%</t>
+          <t>-175.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73.2%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-169.2%</t>
+          <t>-187.8%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-90.3%</t>
+          <t>-109.1%</t>
         </is>
       </c>
     </row>
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.4214543533367376</v>
+        <v>0.1102648519860253</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.303060395440507</v>
+        <v>3.178584594900222</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.817565989731229</v>
+        <v>1.506376488380516</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.225374672258297</v>
+        <v>4.03866097144787</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.3556869632873255</v>
+        <v>0.04449746193661325</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.277771048551212</v>
+        <v>3.153295248010928</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.817565989731229</v>
+        <v>1.506376488380516</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.226392281388767</v>
+        <v>4.03967858057834</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.3421514795106159</v>
+        <v>0.03096197815990365</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.262984887028284</v>
+        <v>3.138509086487999</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.817565989731229</v>
+        <v>1.506376488380516</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.217020313376523</v>
+        <v>4.030306612566095</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.2603795790828642</v>
+        <v>-0.05080992226784803</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.220358852812422</v>
+        <v>3.095883052272137</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.844601563137365</v>
+        <v>1.533412061786653</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.223324383375443</v>
+        <v>4.036610682565016</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.1931704712109866</v>
+        <v>-0.1180190301397257</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.198240526497373</v>
+        <v>3.073764725957088</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.844601563137365</v>
+        <v>1.533412061786653</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.228089700209145</v>
+        <v>4.041375999398718</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.1971619240061768</v>
+        <v>-0.1140275773445355</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.19766190373469</v>
+        <v>3.073186103194405</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.848593015932555</v>
+        <v>1.537403514581843</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.228309368005499</v>
+        <v>4.041595667195073</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.2009865069470839</v>
+        <v>-0.5121760082977962</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.036329422858449</v>
+        <v>2.911853622318163</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.450444584979295</v>
+        <v>1.139255083628583</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.987347200938607</v>
+        <v>3.800633500128179</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.4226084405052014</v>
+        <v>-0.7337979418559137</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.947546866034124</v>
+        <v>2.823071065493838</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.412918451291926</v>
+        <v>1.101728949941214</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.964697737325107</v>
+        <v>3.77798403651468</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.6306124988582786</v>
+        <v>-0.941802000208991</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.869237387246818</v>
+        <v>2.744761586706533</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.412918451291926</v>
+        <v>1.101728949941214</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.969589881879032</v>
+        <v>3.782876181068605</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.901012461567164</v>
+        <v>-1.212201962917876</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.756158858501252</v>
+        <v>2.631683057960967</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.14251848858304</v>
+        <v>0.8313289872323282</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.802431360591689</v>
+        <v>3.615717659781262</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.240170839155686</v>
+        <v>-1.551360340506398</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.613579806772292</v>
+        <v>2.489104006232007</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.8033601109945183</v>
+        <v>0.4921706096438061</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.592020633345025</v>
+        <v>3.405306932534597</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.568188060883165</v>
+        <v>-1.879377562233877</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.502711207820068</v>
+        <v>2.378235407279784</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4753428892670392</v>
+        <v>0.1641533879163269</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.415548590047305</v>
+        <v>3.228834889236878</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.564851314374194</v>
+        <v>-1.876040815724906</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.512144656832226</v>
+        <v>2.387668856291941</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.4780349216860705</v>
+        <v>0.1668454203353583</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.425262559907293</v>
+        <v>3.238548859096866</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.931562366040739</v>
+        <v>-2.242751867391451</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.366566628209339</v>
+        <v>2.242090827669055</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.1113238700195249</v>
+        <v>-0.1998656313311873</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.206342320951098</v>
+        <v>3.01962862014067</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.316742756970812</v>
+        <v>-2.627932258321524</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.211037010650174</v>
+        <v>2.086561210109889</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.1113238700195249</v>
+        <v>-0.1998656313311873</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.204884859763961</v>
+        <v>3.018171158953534</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.660425530197474</v>
+        <v>-2.971615031548187</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.075333024814125</v>
+        <v>1.95085722427384</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.003417817992306726</v>
+        <v>-0.3077716833584055</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.141910352002246</v>
+        <v>2.955196651191819</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.018075880435823</v>
+        <v>-3.329265381786535</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.928378943375043</v>
+        <v>1.803903142834758</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.3542325322460414</v>
+        <v>-0.6654220335967536</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.923426200515495</v>
+        <v>2.736712499705068</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.02473682065797</v>
+        <v>-3.335926322008683</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.927487493986444</v>
+        <v>1.803011693446159</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.3542325322460414</v>
+        <v>-0.6654220335967536</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.925199127215755</v>
+        <v>2.738485426405328</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.456542613807758</v>
+        <v>-3.76773211515847</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.741098064193933</v>
+        <v>1.616622263653648</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4906500286873084</v>
+        <v>-0.8018395300380206</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.829681516818399</v>
+        <v>2.642967816007972</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.782975142675502</v>
+        <v>-4.094164644026215</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.598809827648927</v>
+        <v>1.474334027108641</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.5731182791944566</v>
+        <v>-0.8843077805451687</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.768485341516201</v>
+        <v>2.581771640705774</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.784539293785805</v>
+        <v>-4.095728795136518</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.596764758860771</v>
+        <v>1.472288958320485</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.5731182791944566</v>
+        <v>-0.8843077805451687</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.767065933172166</v>
+        <v>2.580352232361739</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.148165538686118</v>
+        <v>-4.459355040036831</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.457801821134887</v>
+        <v>1.333326020594602</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.6713399160615824</v>
+        <v>-0.9825294174122945</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.714620511286132</v>
+        <v>2.527906810475705</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.145738474157399</v>
+        <v>-4.456927975508113</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.458027161952206</v>
+        <v>1.33355136141192</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.671672697868734</v>
+        <v>-0.9828621992194462</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.713675357207673</v>
+        <v>2.526961656397245</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.554327251338078</v>
+        <v>-4.865516752688791</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.293353195094693</v>
+        <v>1.168877394554408</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.391450976400125</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.467283634914025</v>
+        <v>2.280569934103597</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.967309735479172</v>
+        <v>-5.278499236829885</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.123345633909716</v>
+        <v>0.9988698333694312</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.391450976400125</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.462469067385485</v>
+        <v>2.275755366575058</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.383701609766169</v>
+        <v>-5.694891111116882</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9547829348037946</v>
+        <v>0.8303071342635095</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.391450976400125</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.460463117994363</v>
+        <v>2.273749417183935</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.760378620296014</v>
+        <v>-6.071568121646727</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.8143708212605358</v>
+        <v>0.6898950207202508</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.391450976400125</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.470721808663042</v>
+        <v>2.284008107852614</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.774093484621125</v>
+        <v>-6.085282985971838</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.8049844406761864</v>
+        <v>0.6805086401359013</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.391450976400125</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.466821373808737</v>
+        <v>2.28010767299831</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.086918283866105</v>
+        <v>-6.398107785216817</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6782594410331955</v>
+        <v>0.5537836404929104</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.391450976400125</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.465226293863738</v>
+        <v>2.278512593053311</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.091731322331442</v>
+        <v>-6.402920823682154</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.680113201576269</v>
+        <v>0.5556374010359839</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.39299761110291</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.468077288971275</v>
+        <v>2.281363588160847</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.525080430441678</v>
+        <v>-6.836269931792391</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.5027472537977715</v>
+        <v>0.3782714532574865</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.39299761110291</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.464050984436871</v>
+        <v>2.277337283626444</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.908081819184309</v>
+        <v>-7.219271320535022</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.3494445969791347</v>
+        <v>0.2249687964388496</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.39299761110291</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.463948883115287</v>
+        <v>2.27723518230486</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.283067145355586</v>
+        <v>-7.594256646706299</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.2020219824820542</v>
+        <v>0.0775461819417691</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.456793435923476</v>
+        <v>-1.767982937274188</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.241529203383951</v>
+        <v>2.054815502573524</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.642597467859588</v>
+        <v>-7.9537869692103</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.0635601567785038</v>
+        <v>-0.06091564376178127</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.456793435923476</v>
+        <v>-1.767982937274188</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.246879506682001</v>
+        <v>2.060165805871573</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.968997496524601</v>
+        <v>-8.280186997875314</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.05908383473032419</v>
+        <v>-0.1835596352706093</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.783193464588488</v>
+        <v>-2.094382965939201</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.058955509440171</v>
+        <v>1.872241808629744</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.962521349731041</v>
+        <v>-8.273710851081754</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.05345162539113124</v>
+        <v>-0.1779274259314163</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.776717317794929</v>
+        <v>-2.087906819145641</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.065882948138076</v>
+        <v>1.879169247327648</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.95883042477463</v>
+        <v>-8.270019926125343</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.05197525540856685</v>
+        <v>-0.1764510559488524</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.776717317794929</v>
+        <v>-2.087906819145641</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.065882948138076</v>
+        <v>1.879169247327648</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.163088600104492</v>
+        <v>-8.474278101455207</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1281653284218693</v>
+        <v>-0.2526411289621553</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.904356262408918</v>
+        <v>-2.21554576375963</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.994812778488325</v>
+        <v>1.808099077677897</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.323727626592857</v>
+        <v>-8.634917127943572</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1879383845327793</v>
+        <v>-0.3124141850730653</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.019089735411313</v>
+        <v>-2.330279236762026</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.930455249171323</v>
+        <v>1.743741548360896</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.250257794925409</v>
+        <v>-8.561447296276123</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1431787503723787</v>
+        <v>-0.2676545509126647</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.945619903743865</v>
+        <v>-2.256809405094577</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.989908849665214</v>
+        <v>1.803195148854786</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.425382212311952</v>
+        <v>-8.736571713662666</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.1986732965794795</v>
+        <v>-0.323149097119765</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.120744321130409</v>
+        <v>-2.431933822481121</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.899389419980804</v>
+        <v>1.712675719170377</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.659834306326442</v>
+        <v>-8.971023807677156</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.2996732990868711</v>
+        <v>-0.4241490996271571</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.120744321130409</v>
+        <v>-2.431933822481121</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.892170255079208</v>
+        <v>1.705456554268781</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.94763815086368</v>
+        <v>-9.258827652214395</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4214670276757428</v>
+        <v>-0.5459428282160288</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.408548165667647</v>
+        <v>-2.719737667018359</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.712815757582889</v>
+        <v>1.526102056772461</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.177462598027505</v>
+        <v>-9.48865209937822</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5122810167027163</v>
+        <v>-0.6367568172430023</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.571195702737807</v>
+        <v>-2.88238520408852</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.616343025179349</v>
+        <v>1.429629324368922</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.114393365721165</v>
+        <v>-9.42558286707188</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.4843595951510657</v>
+        <v>-0.6088353956913517</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.599709265420042</v>
+        <v>-2.910898766770754</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.601928616199123</v>
+        <v>1.415214915388695</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.062377851752352</v>
+        <v>-9.373567353103066</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4595630538771398</v>
+        <v>-0.5840388544174253</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.599709265420042</v>
+        <v>-2.910898766770754</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.605918951885524</v>
+        <v>1.419205251075096</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.143669781306556</v>
+        <v>-9.454859282657271</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.4935550525975634</v>
+        <v>-0.6180308531378489</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.599709265420042</v>
+        <v>-2.910898766770754</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.604443724986782</v>
+        <v>1.417730024176355</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.946400375578559</v>
+        <v>-9.257589876929273</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.399593880141492</v>
+        <v>-0.5240696806817779</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.402439859692044</v>
+        <v>-2.713629361042756</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.737858778588453</v>
+        <v>1.551145077778026</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.74724826834146</v>
+        <v>-9.058437769692175</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.3329841708933352</v>
+        <v>-0.4574599714336212</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.23711733374223</v>
+        <v>-2.548306835092943</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.824001160511658</v>
+        <v>1.637287459701231</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.52140311562205</v>
+        <v>-8.832592616972764</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.2330670367693628</v>
+        <v>-0.3575428373096483</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.195190658155067</v>
+        <v>-2.506380159505779</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.858736238900165</v>
+        <v>1.672022538089738</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.235128303299355</v>
+        <v>-8.546317804650069</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.1174179672842257</v>
+        <v>-0.2418937678245117</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.195190658155067</v>
+        <v>-2.506380159505779</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.859875383456224</v>
+        <v>1.673161682645796</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.008332476226022</v>
+        <v>-8.319521977576736</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.02406586229278496</v>
+        <v>-0.1485416628330705</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.127076713533522</v>
+        <v>-2.438266214884234</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.903377524391258</v>
+        <v>1.716663823580831</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-7.724423745297273</v>
+        <v>-8.035613246647987</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.0952313343173512</v>
+        <v>-0.02924446622293431</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.127076713533522</v>
+        <v>-2.438266214884234</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.909111228629895</v>
+        <v>1.722397527819467</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-7.47743649510432</v>
+        <v>-7.788625996455035</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.1842889720006671</v>
+        <v>0.05981317146038112</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.88008946334057</v>
+        <v>-2.191278964691282</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.047566316351801</v>
+        <v>1.860852615541373</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-7.213599627900251</v>
+        <v>-7.524789129250966</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.2799402375693871</v>
+        <v>0.1554644370291012</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.88008946334057</v>
+        <v>-2.191278964691282</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.037682835038893</v>
+        <v>1.850969134228466</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.946357827031854</v>
+        <v>-7.257547328382569</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.385002397417372</v>
+        <v>0.2605265968770865</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.88008946334057</v>
+        <v>-2.191278964691282</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.03584827453952</v>
+        <v>1.849134573729092</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.67054866363137</v>
+        <v>-6.981738164982085</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.4950257478041049</v>
+        <v>0.370549947263819</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.791070155061837</v>
+        <v>-2.102259656412549</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.088959544533298</v>
+        <v>1.902245843722871</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.401481075864391</v>
+        <v>-6.712670577215105</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.6033212890563902</v>
+        <v>0.4788454885161046</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.522002567294857</v>
+        <v>-1.83319206864557</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.25106860333898</v>
+        <v>2.064354902528553</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.137421137541595</v>
+        <v>-6.448610638892309</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.6956849482237564</v>
+        <v>0.5712091476834709</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.257942628972061</v>
+        <v>-1.569132130322773</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.396244250170906</v>
+        <v>2.209530549360478</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-5.430341514036757</v>
+        <v>-5.741531015387471</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.9757297639653912</v>
+        <v>0.8512539634251053</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.257942628972061</v>
+        <v>-1.569132130322773</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.393457216510605</v>
+        <v>2.206743515700177</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-5.180700484050805</v>
+        <v>-5.491889985401519</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.075929799847613</v>
+        <v>0.9514539993073274</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.008301598986109</v>
+        <v>-1.319491100336822</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.543585458390017</v>
+        <v>2.35687175757959</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.926158584709729</v>
+        <v>-5.237348086060443</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.1771133808048</v>
+        <v>1.052637580264515</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.753759699645034</v>
+        <v>-1.064949200995746</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.695677419215419</v>
+        <v>2.508963718404992</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-4.69267736248013</v>
+        <v>-5.003866863830845</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.278430298534492</v>
+        <v>1.153954497994206</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5202784774154354</v>
+        <v>-0.8314679787661476</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.84369058139103</v>
+        <v>2.656976880580603</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.512968832336258</v>
+        <v>-4.824158333686972</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.347421500279082</v>
+        <v>1.222945699738796</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4631069732527393</v>
+        <v>-0.7742964746034515</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.875101273575689</v>
+        <v>2.688387572765262</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.380693358705371</v>
+        <v>-4.691882860056086</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.395699176478464</v>
+        <v>1.271223375938178</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.3308314996218527</v>
+        <v>-0.6420210009725649</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.949834044501248</v>
+        <v>2.763120343690821</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.190093684032218</v>
+        <v>-4.501283185382933</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.474754107035362</v>
+        <v>1.350278306495076</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1402318249486998</v>
+        <v>-0.451421326299412</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.067008909992777</v>
+        <v>2.880295209182349</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.941093885348638</v>
+        <v>-4.252283386699352</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.587260367732453</v>
+        <v>1.462784567192167</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.1087679737348809</v>
+        <v>-0.2024215276158313</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.229315130426584</v>
+        <v>3.042601429616156</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-3.749714810487698</v>
+        <v>-4.060904311838412</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.53583606807761</v>
+        <v>1.411360267537324</v>
       </c>
       <c r="F1908" t="n">
-        <v>0.300147048595821</v>
+        <v>-0.01104245275489124</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.216166645743929</v>
+        <v>3.029452944933502</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-3.470687514832071</v>
+        <v>-3.781877016182785</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.695991328216947</v>
+        <v>1.571515527676661</v>
       </c>
       <c r="F1909" t="n">
-        <v>0.300147048595821</v>
+        <v>-0.01104245275489124</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.264710987621016</v>
+        <v>3.077997286810588</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-3.193949340161259</v>
+        <v>-3.505138841511972</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.810065610071267</v>
+        <v>1.685589809530981</v>
       </c>
       <c r="F1910" t="n">
-        <v>0.4819637097057468</v>
+        <v>0.1707742083550345</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.377179996272965</v>
+        <v>3.190466295462538</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-3.067056933726189</v>
+        <v>-3.378246435076902</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.852108586391816</v>
+        <v>1.727632785851531</v>
       </c>
       <c r="F1911" t="n">
-        <v>0.6088561161408167</v>
+        <v>0.2976666147901045</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.444601453880529</v>
+        <v>3.257887753070102</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-2.879469425816262</v>
+        <v>-3.190658927166976</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.920182977460694</v>
+        <v>1.795707176920408</v>
       </c>
       <c r="F1912" t="n">
-        <v>0.6088561161408167</v>
+        <v>0.2976666147901045</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.437640841785436</v>
+        <v>3.250927140975009</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-2.637321032362404</v>
+        <v>-2.948510533713117</v>
       </c>
       <c r="E1913" t="n">
-        <v>2.031504689223381</v>
+        <v>1.907028888683095</v>
       </c>
       <c r="F1913" t="n">
-        <v>0.6088561161408167</v>
+        <v>0.2976666147901045</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.452103196166579</v>
+        <v>3.265389495356152</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-2.574091660594056</v>
+        <v>-2.885281161944769</v>
       </c>
       <c r="E1914" t="n">
-        <v>2.051328558389915</v>
+        <v>1.92685275784963</v>
       </c>
       <c r="F1914" t="n">
-        <v>0.6088561161408167</v>
+        <v>0.2976666147901045</v>
       </c>
       <c r="G1914" t="n">
-        <v>3.446635316625774</v>
+        <v>3.259921615815347</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.486558612509469</v>
+        <v>3.549108959973533</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-2.385611703600269</v>
+        <v>-2.698793469567763</v>
       </c>
       <c r="E1915" t="n">
-        <v>2.124218635198006</v>
+        <v>1.998945928811009</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.7973360731346035</v>
+        <v>0.4841543071671107</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.557221384832623</v>
+        <v>3.369312325252128</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240327.xlsx
+++ b/tame_output/ON/bt/strategyON_20240327.xlsx
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.74769908470241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309725</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858727</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096472</v>
+        <v>3.856158176096474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430984</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69292828007764</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457898</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879199</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568103</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963415</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192813</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.549108959973533</v>
+        <v>3.549108959973537</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>

--- a/tame_output/ON/bt/strategyON_20240327.xlsx
+++ b/tame_output/ON/bt/strategyON_20240327.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,25 +801,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-27.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-22.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-69.5%</t>
+          <t>-70.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>107.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>124.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-571.0%</t>
+          <t>-569.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-64.5%</t>
+          <t>-66.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>908.0%</t>
+          <t>747.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-431.5%</t>
+          <t>-448.8%</t>
         </is>
       </c>
     </row>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-228.8%</t>
+          <t>-228.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.4%</t>
+          <t>-35.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-50.6%</t>
+          <t>-50.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-29.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-176.3%</t>
+          <t>-183.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,11 +1289,11 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-312.4%</t>
+          <t>-310.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-32.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-13.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.2%</t>
+          <t>-159.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-175.6%</t>
+          <t>-192.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,22 +1418,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,11 +1447,11 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-187.8%</t>
+          <t>-186.8%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-13.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-109.1%</t>
+          <t>-157.2%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1915"/>
+  <dimension ref="A1:G1916"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998562</v>
+        <v>3.367370539998563</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082127</v>
+        <v>3.299560092082128</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.1102648519860253</v>
+        <v>0.1272551002600116</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.178584594900222</v>
+        <v>3.185380694209817</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.506376488380516</v>
+        <v>1.523366736654503</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.03866097144787</v>
+        <v>4.048855120412261</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757925</v>
+        <v>3.293490533757926</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.04449746193661325</v>
+        <v>0.06148771021059951</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.153295248010928</v>
+        <v>3.160091347320522</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.506376488380516</v>
+        <v>1.523366736654503</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.03967858057834</v>
+        <v>4.049872729542732</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760743</v>
+        <v>3.293766719760744</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.03096197815990365</v>
+        <v>0.04795222643388991</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.138509086487999</v>
+        <v>3.145305185797594</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.506376488380516</v>
+        <v>1.523366736654503</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.030306612566095</v>
+        <v>4.040500761530487</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706672</v>
+        <v>3.298730590706673</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.05080992226784803</v>
+        <v>-0.03381967399386177</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.095883052272137</v>
+        <v>3.102679151581731</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.533412061786653</v>
+        <v>1.550402310060639</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.036610682565016</v>
+        <v>4.046804831529407</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296839</v>
+        <v>3.29991811929684</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.1180190301397257</v>
+        <v>-0.1010287818657394</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.073764725957088</v>
+        <v>3.080560825266683</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.533412061786653</v>
+        <v>1.550402310060639</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.041375999398718</v>
+        <v>4.05157014836311</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201489</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.1140275773445355</v>
+        <v>-0.09703732907054924</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.073186103194405</v>
+        <v>3.079982202503999</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.537403514581843</v>
+        <v>1.55439376285583</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.041595667195073</v>
+        <v>4.051789816159465</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.5121760082977962</v>
+        <v>-0.4951857600238099</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.911853622318163</v>
+        <v>2.918649721627758</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.139255083628583</v>
+        <v>1.156245331902569</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.800633500128179</v>
+        <v>3.810827649092571</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.7337979418559137</v>
+        <v>-0.7168076935819274</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.823071065493838</v>
+        <v>2.829867164803433</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.101728949941214</v>
+        <v>1.1187191982152</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.77798403651468</v>
+        <v>3.788178185479071</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.941802000208991</v>
+        <v>-0.9248117519350046</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.744761586706533</v>
+        <v>2.751557686016127</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.101728949941214</v>
+        <v>1.1187191982152</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.782876181068605</v>
+        <v>3.793070330032997</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.212201962917876</v>
+        <v>-1.19521171464389</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.631683057960967</v>
+        <v>2.638479157270561</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.8313289872323282</v>
+        <v>0.8483192355063147</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.615717659781262</v>
+        <v>3.625911808745654</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.551360340506398</v>
+        <v>-1.534370092232412</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.489104006232007</v>
+        <v>2.495900105541601</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.4921706096438061</v>
+        <v>0.5091608579177926</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.405306932534597</v>
+        <v>3.41550108149899</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.879377562233877</v>
+        <v>-1.862387313959891</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.378235407279784</v>
+        <v>2.385031506589378</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.1641533879163269</v>
+        <v>0.1811436361903135</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.228834889236878</v>
+        <v>3.23902903820127</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.876040815724906</v>
+        <v>-1.85905056745092</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.387668856291941</v>
+        <v>2.394464955601535</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.1668454203353583</v>
+        <v>0.1838356686093449</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.238548859096866</v>
+        <v>3.248743008061258</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.242751867391451</v>
+        <v>-2.225761619117465</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.242090827669055</v>
+        <v>2.248886926978649</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1998656313311873</v>
+        <v>-0.1828753830572007</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.01962862014067</v>
+        <v>3.029822769105063</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.627932258321524</v>
+        <v>-2.610942010047538</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.086561210109889</v>
+        <v>2.093357309419484</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1998656313311873</v>
+        <v>-0.1828753830572007</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.018171158953534</v>
+        <v>3.028365307917926</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.971615031548187</v>
+        <v>-2.954624783274201</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.95085722427384</v>
+        <v>1.957653323583434</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.3077716833584055</v>
+        <v>-0.2907814350844189</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.955196651191819</v>
+        <v>2.965390800156211</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.329265381786535</v>
+        <v>-3.312275133512549</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.803903142834758</v>
+        <v>1.810699242144353</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6654220335967536</v>
+        <v>-0.648431785322767</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.736712499705068</v>
+        <v>2.74690664866946</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.335926322008683</v>
+        <v>-3.318936073734696</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.803011693446159</v>
+        <v>1.809807792755753</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6654220335967536</v>
+        <v>-0.648431785322767</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.738485426405328</v>
+        <v>2.74867957536972</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.76773211515847</v>
+        <v>-3.750741866884484</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.616622263653648</v>
+        <v>1.623418362963243</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8018395300380206</v>
+        <v>-0.784849281764034</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.642967816007972</v>
+        <v>2.653161964972364</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.094164644026215</v>
+        <v>-4.077174395752229</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.474334027108641</v>
+        <v>1.481130126418236</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8843077805451687</v>
+        <v>-0.8673175322711821</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.581771640705774</v>
+        <v>2.591965789670166</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.095728795136518</v>
+        <v>-4.078738546862532</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.472288958320485</v>
+        <v>1.47908505763008</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8843077805451687</v>
+        <v>-0.8673175322711821</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.580352232361739</v>
+        <v>2.59054638132613</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.459355040036831</v>
+        <v>-4.442364791762845</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.333326020594602</v>
+        <v>1.340122119904196</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9825294174122945</v>
+        <v>-0.965539169138308</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.527906810475705</v>
+        <v>2.538100959440097</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.456927975508113</v>
+        <v>-4.439937727234127</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.33355136141192</v>
+        <v>1.340347460721515</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.9828621992194462</v>
+        <v>-0.9658719509454596</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.526961656397245</v>
+        <v>2.537155805361637</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.865516752688791</v>
+        <v>-4.848526504414805</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.168877394554408</v>
+        <v>1.175673493864003</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.391450976400125</v>
+        <v>-1.374460728126138</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.280569934103597</v>
+        <v>2.290764083067989</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.278499236829885</v>
+        <v>-5.261508988555899</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.9988698333694312</v>
+        <v>1.005665932679026</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.391450976400125</v>
+        <v>-1.374460728126138</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.275755366575058</v>
+        <v>2.28594951553945</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.694891111116882</v>
+        <v>-5.677900862842896</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.8303071342635095</v>
+        <v>0.8371032335731039</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.391450976400125</v>
+        <v>-1.374460728126138</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.273749417183935</v>
+        <v>2.283943566148327</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.071568121646727</v>
+        <v>-6.05457787337274</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.6898950207202508</v>
+        <v>0.6966911200298451</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.391450976400125</v>
+        <v>-1.374460728126138</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.284008107852614</v>
+        <v>2.294202256817006</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.085282985971838</v>
+        <v>-6.068292737697852</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.6805086401359013</v>
+        <v>0.6873047394454956</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.391450976400125</v>
+        <v>-1.374460728126138</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.28010767299831</v>
+        <v>2.290301821962701</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.398107785216817</v>
+        <v>-6.381117536942831</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.5537836404929104</v>
+        <v>0.5605797398025048</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.391450976400125</v>
+        <v>-1.374460728126138</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.278512593053311</v>
+        <v>2.288706742017702</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.402920823682154</v>
+        <v>-6.385930575408168</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.5556374010359839</v>
+        <v>0.5624335003455783</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.39299761110291</v>
+        <v>-1.376007362828924</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.281363588160847</v>
+        <v>2.291557737125239</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.836269931792391</v>
+        <v>-6.819279683518404</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.3782714532574865</v>
+        <v>0.3850675525670808</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.39299761110291</v>
+        <v>-1.376007362828924</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.277337283626444</v>
+        <v>2.287531432590836</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.219271320535022</v>
+        <v>-7.202281072261036</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.2249687964388496</v>
+        <v>0.2317648957484444</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.39299761110291</v>
+        <v>-1.376007362828924</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.27723518230486</v>
+        <v>2.287429331269252</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.594256646706299</v>
+        <v>-7.577266398432313</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.0775461819417691</v>
+        <v>0.08434228125136345</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.767982937274188</v>
+        <v>-1.750992689000201</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.054815502573524</v>
+        <v>2.065009651537915</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.9537869692103</v>
+        <v>-7.936796720936314</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.06091564376178127</v>
+        <v>-0.05411954445218692</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.767982937274188</v>
+        <v>-1.750992689000201</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.060165805871573</v>
+        <v>2.070359954835966</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.280186997875314</v>
+        <v>-8.263196749601327</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1835596352706093</v>
+        <v>-0.1767635359610149</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.094382965939201</v>
+        <v>-2.077392717665214</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.872241808629744</v>
+        <v>1.882435957594135</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.273710851081754</v>
+        <v>-8.256720602807768</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1779274259314163</v>
+        <v>-0.171131326621822</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.087906819145641</v>
+        <v>-2.070916570871654</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.879169247327648</v>
+        <v>1.88936339629204</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.270019926125343</v>
+        <v>-8.253029677851357</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1764510559488524</v>
+        <v>-0.1696549566392576</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.087906819145641</v>
+        <v>-2.070916570871654</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.879169247327648</v>
+        <v>1.88936339629204</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.474278101455207</v>
+        <v>-8.457287853181221</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2526411289621553</v>
+        <v>-0.2458450296525609</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.21554576375963</v>
+        <v>-2.198555515485643</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.808099077677897</v>
+        <v>1.818293226642289</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.634917127943572</v>
+        <v>-8.617926879669586</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3124141850730653</v>
+        <v>-0.3056180857634709</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.330279236762026</v>
+        <v>-2.313288988488039</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.743741548360896</v>
+        <v>1.753935697325288</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.561447296276123</v>
+        <v>-8.544457048002137</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2676545509126647</v>
+        <v>-0.2608584516030703</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.256809405094577</v>
+        <v>-2.239819156820591</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.803195148854786</v>
+        <v>1.813389297819178</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.736571713662666</v>
+        <v>-8.71958146538868</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.323149097119765</v>
+        <v>-0.3163529978101707</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.431933822481121</v>
+        <v>-2.414943574207134</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.712675719170377</v>
+        <v>1.722869868134769</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.971023807677156</v>
+        <v>-8.95403355940317</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4241490996271571</v>
+        <v>-0.4173530003175627</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.431933822481121</v>
+        <v>-2.414943574207134</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.705456554268781</v>
+        <v>1.715650703233172</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.258827652214395</v>
+        <v>-9.241837403940409</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5459428282160288</v>
+        <v>-0.539146728906434</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.719737667018359</v>
+        <v>-2.702747418744373</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.526102056772461</v>
+        <v>1.536296205736853</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.48865209937822</v>
+        <v>-9.471661851104233</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6367568172430023</v>
+        <v>-0.6299607179334079</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.88238520408852</v>
+        <v>-2.865394955814533</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.429629324368922</v>
+        <v>1.439823473333313</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.42558286707188</v>
+        <v>-9.408592618797893</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6088353956913517</v>
+        <v>-0.6020392963817573</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.910898766770754</v>
+        <v>-2.893908518496767</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.415214915388695</v>
+        <v>1.425409064353087</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.373567353103066</v>
+        <v>-9.35657710482908</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5840388544174253</v>
+        <v>-0.577242755107831</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.910898766770754</v>
+        <v>-2.893908518496767</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.419205251075096</v>
+        <v>1.429399400039488</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.454859282657271</v>
+        <v>-9.437869034383285</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6180308531378489</v>
+        <v>-0.6112347538282545</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.910898766770754</v>
+        <v>-2.893908518496767</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.417730024176355</v>
+        <v>1.427924173140747</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.257589876929273</v>
+        <v>-9.240599628655287</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5240696806817779</v>
+        <v>-0.5172735813721832</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.713629361042756</v>
+        <v>-2.696639112768769</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.551145077778026</v>
+        <v>1.561339226742418</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.058437769692175</v>
+        <v>-9.041447521418188</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4574599714336212</v>
+        <v>-0.4506638721240268</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.548306835092943</v>
+        <v>-2.531316586818956</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.637287459701231</v>
+        <v>1.647481608665623</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.832592616972764</v>
+        <v>-8.815602368698777</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3575428373096483</v>
+        <v>-0.3507467380000535</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.506380159505779</v>
+        <v>-2.489389911231792</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.672022538089738</v>
+        <v>1.68221668705413</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.546317804650069</v>
+        <v>-8.529327556376082</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.2418937678245117</v>
+        <v>-0.2350976685149164</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.506380159505779</v>
+        <v>-2.489389911231792</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.673161682645796</v>
+        <v>1.683355831610188</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.319521977576736</v>
+        <v>-8.302531729302748</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.1485416628330705</v>
+        <v>-0.1417455635234752</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.438266214884234</v>
+        <v>-2.421275966610248</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.716663823580831</v>
+        <v>1.726857972545223</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.035613246647987</v>
+        <v>-8.018622998373999</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.02924446622293431</v>
+        <v>-0.02244836691333951</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.438266214884234</v>
+        <v>-2.421275966610248</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.722397527819467</v>
+        <v>1.732591676783859</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-7.788625996455035</v>
+        <v>-7.771635748181047</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.05981317146038112</v>
+        <v>0.06660927076997636</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.191278964691282</v>
+        <v>-2.174288716417296</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.860852615541373</v>
+        <v>1.871046764505765</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74769908470241</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-7.524789129250966</v>
+        <v>-7.507798880976978</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.1554644370291012</v>
+        <v>0.1622605363386964</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.191278964691282</v>
+        <v>-2.174288716417296</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.850969134228466</v>
+        <v>1.861163283192858</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.257547328382569</v>
+        <v>-7.240557080108581</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.2605265968770865</v>
+        <v>0.2673226961866813</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.191278964691282</v>
+        <v>-2.174288716417296</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.849134573729092</v>
+        <v>1.859328722693484</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.981738164982085</v>
+        <v>-6.964747916708097</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.370549947263819</v>
+        <v>0.3773460465734142</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.102259656412549</v>
+        <v>-2.085269408138562</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.902245843722871</v>
+        <v>1.912439992687263</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.712670577215105</v>
+        <v>-6.695680328941117</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.4788454885161046</v>
+        <v>0.4856415878256999</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.83319206864557</v>
+        <v>-1.816201820371583</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.064354902528553</v>
+        <v>2.074549051492944</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.448610638892309</v>
+        <v>-6.431620390618321</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.5712091476834709</v>
+        <v>0.5780052469930661</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.569132130322773</v>
+        <v>-1.552141882048787</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.209530549360478</v>
+        <v>2.21972469832487</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309728</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-5.741531015387471</v>
+        <v>-5.724540767113483</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.8512539634251053</v>
+        <v>0.8580500627347005</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.569132130322773</v>
+        <v>-1.552141882048787</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.206743515700177</v>
+        <v>2.216937664664569</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-5.491889985401519</v>
+        <v>-5.474899737127531</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.9514539993073274</v>
+        <v>0.9582500986169227</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.319491100336822</v>
+        <v>-1.302500852062835</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.35687175757959</v>
+        <v>2.367065906543981</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096474</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.237348086060443</v>
+        <v>-5.220357837786455</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.052637580264515</v>
+        <v>1.05943367957411</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.064949200995746</v>
+        <v>-1.04795895272176</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.508963718404992</v>
+        <v>2.519157867369384</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.003866863830845</v>
+        <v>-4.986876615556857</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.153954497994206</v>
+        <v>1.160750597303802</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8314679787661476</v>
+        <v>-0.8144777304921611</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.656976880580603</v>
+        <v>2.667171029544996</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.824158333686972</v>
+        <v>-4.807168085412984</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.222945699738796</v>
+        <v>1.229741799048392</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7742964746034515</v>
+        <v>-0.757306226329465</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.688387572765262</v>
+        <v>2.698581721729654</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.691882860056086</v>
+        <v>-4.674892611782098</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.271223375938178</v>
+        <v>1.278019475247773</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6420210009725649</v>
+        <v>-0.6250307526985783</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.763120343690821</v>
+        <v>2.773314492655213</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.501283185382933</v>
+        <v>-4.484292937108945</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.350278306495076</v>
+        <v>1.357074405804671</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.451421326299412</v>
+        <v>-0.4344310780254255</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.880295209182349</v>
+        <v>2.890489358146741</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.252283386699352</v>
+        <v>-4.235293138425364</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.462784567192167</v>
+        <v>1.469580666501762</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2024215276158313</v>
+        <v>-0.1854312793418448</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.042601429616156</v>
+        <v>3.052795578580549</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-4.060904311838412</v>
+        <v>-4.043914063564424</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.411360267537324</v>
+        <v>1.418156366846919</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.01104245275489124</v>
+        <v>0.0059477955190953</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.029452944933502</v>
+        <v>3.039647093897894</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-3.781877016182785</v>
+        <v>-3.764886767908797</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.571515527676661</v>
+        <v>1.578311626986257</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.01104245275489124</v>
+        <v>0.0059477955190953</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.077997286810588</v>
+        <v>3.08819143577498</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-3.505138841511972</v>
+        <v>-3.488148593237984</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.685589809530981</v>
+        <v>1.692385908840576</v>
       </c>
       <c r="F1910" t="n">
-        <v>0.1707742083550345</v>
+        <v>0.1877644566290211</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.190466295462538</v>
+        <v>3.20066044442693</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-3.378246435076902</v>
+        <v>-3.361256186802914</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.727632785851531</v>
+        <v>1.734428885161126</v>
       </c>
       <c r="F1911" t="n">
-        <v>0.2976666147901045</v>
+        <v>0.314656863064091</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.257887753070102</v>
+        <v>3.268081902034494</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-3.190658927166976</v>
+        <v>-3.173668678892988</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.795707176920408</v>
+        <v>1.802503276230004</v>
       </c>
       <c r="F1912" t="n">
-        <v>0.2976666147901045</v>
+        <v>0.314656863064091</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.250927140975009</v>
+        <v>3.261121289939401</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-2.948510533713117</v>
+        <v>-2.93152028543913</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.907028888683095</v>
+        <v>1.91382498799269</v>
       </c>
       <c r="F1913" t="n">
-        <v>0.2976666147901045</v>
+        <v>0.314656863064091</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.265389495356152</v>
+        <v>3.275583644320544</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-2.885281161944769</v>
+        <v>-2.868290913670781</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.92685275784963</v>
+        <v>1.933648857159224</v>
       </c>
       <c r="F1914" t="n">
-        <v>0.2976666147901045</v>
+        <v>0.314656863064091</v>
       </c>
       <c r="G1914" t="n">
-        <v>3.259921615815347</v>
+        <v>3.270115764779739</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,45 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.549108959973537</v>
+        <v>3.828049353262046</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-2.698793469567763</v>
+        <v>-2.87224532576084</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.998945928811009</v>
+        <v>1.929565186333778</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.4841543071671107</v>
+        <v>0.3107024509740327</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.369312325252128</v>
+        <v>3.265241211536281</v>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" s="2" t="n">
+        <v>45378</v>
+      </c>
+      <c r="B1916" t="n">
+        <v>3.54896982266024</v>
+      </c>
+      <c r="C1916" t="n">
+        <v>2.895626040749816</v>
+      </c>
+      <c r="D1916" t="n">
+        <v>-2.87224532576084</v>
+      </c>
+      <c r="E1916" t="n">
+        <v>1.929565186333778</v>
+      </c>
+      <c r="F1916" t="n">
+        <v>0.3107024509740327</v>
+      </c>
+      <c r="G1916" t="n">
+        <v>2.888689837736183</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240327.xlsx
+++ b/tame_output/ON/bt/strategyON_20240327.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.3%</t>
+          <t>-69.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.6%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.1%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-569.3%</t>
+          <t>-571.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.0%</t>
+          <t>-65.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>747.3%</t>
+          <t>908.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-448.8%</t>
+          <t>-431.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-228.1%</t>
+          <t>-228.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.3%</t>
+          <t>-35.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-50.4%</t>
+          <t>-50.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-29.0%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-183.3%</t>
+          <t>-176.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-310.7%</t>
+          <t>-312.4%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.0%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.3%</t>
+          <t>-10.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-159.6%</t>
+          <t>-160.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-192.9%</t>
+          <t>-175.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-186.8%</t>
+          <t>-187.8%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.9%</t>
+          <t>-14.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998563</v>
+        <v>3.367370539998562</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082128</v>
+        <v>3.299560092082127</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.1272551002600116</v>
+        <v>0.1102648519860253</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.185380694209817</v>
+        <v>3.178584594900222</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.523366736654503</v>
+        <v>1.506376488380516</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.048855120412261</v>
+        <v>4.03866097144787</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757926</v>
+        <v>3.293490533757925</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.06148771021059951</v>
+        <v>0.04449746193661325</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.160091347320522</v>
+        <v>3.153295248010928</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.523366736654503</v>
+        <v>1.506376488380516</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.049872729542732</v>
+        <v>4.03967858057834</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760744</v>
+        <v>3.293766719760743</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.04795222643388991</v>
+        <v>0.03096197815990365</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.145305185797594</v>
+        <v>3.138509086487999</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.523366736654503</v>
+        <v>1.506376488380516</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.040500761530487</v>
+        <v>4.030306612566095</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706673</v>
+        <v>3.298730590706672</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.03381967399386177</v>
+        <v>-0.05080992226784803</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.102679151581731</v>
+        <v>3.095883052272137</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.550402310060639</v>
+        <v>1.533412061786653</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.046804831529407</v>
+        <v>4.036610682565016</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.29991811929684</v>
+        <v>3.299918119296839</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.1010287818657394</v>
+        <v>-0.1180190301397257</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.080560825266683</v>
+        <v>3.073764725957088</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.550402310060639</v>
+        <v>1.533412061786653</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.05157014836311</v>
+        <v>4.041375999398718</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201489</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.09703732907054924</v>
+        <v>-0.1140275773445355</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.079982202503999</v>
+        <v>3.073186103194405</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.55439376285583</v>
+        <v>1.537403514581843</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.051789816159465</v>
+        <v>4.041595667195073</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153008</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.4951857600238099</v>
+        <v>-0.5121760082977962</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.918649721627758</v>
+        <v>2.911853622318163</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.156245331902569</v>
+        <v>1.139255083628583</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.810827649092571</v>
+        <v>3.800633500128179</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537427</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.7168076935819274</v>
+        <v>-0.7337979418559137</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.829867164803433</v>
+        <v>2.823071065493838</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.1187191982152</v>
+        <v>1.101728949941214</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.788178185479071</v>
+        <v>3.77798403651468</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.9248117519350046</v>
+        <v>-0.941802000208991</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.751557686016127</v>
+        <v>2.744761586706533</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.1187191982152</v>
+        <v>1.101728949941214</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.793070330032997</v>
+        <v>3.782876181068605</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.19521171464389</v>
+        <v>-1.212201962917876</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.638479157270561</v>
+        <v>2.631683057960967</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.8483192355063147</v>
+        <v>0.8313289872323282</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.625911808745654</v>
+        <v>3.615717659781262</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.534370092232412</v>
+        <v>-1.551360340506398</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.495900105541601</v>
+        <v>2.489104006232007</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5091608579177926</v>
+        <v>0.4921706096438061</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.41550108149899</v>
+        <v>3.405306932534597</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.862387313959891</v>
+        <v>-1.879377562233877</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.385031506589378</v>
+        <v>2.378235407279784</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.1811436361903135</v>
+        <v>0.1641533879163269</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.23902903820127</v>
+        <v>3.228834889236878</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.85905056745092</v>
+        <v>-1.876040815724906</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.394464955601535</v>
+        <v>2.387668856291941</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.1838356686093449</v>
+        <v>0.1668454203353583</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.248743008061258</v>
+        <v>3.238548859096866</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.225761619117465</v>
+        <v>-2.242751867391451</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.248886926978649</v>
+        <v>2.242090827669055</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1828753830572007</v>
+        <v>-0.1998656313311873</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.029822769105063</v>
+        <v>3.01962862014067</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.610942010047538</v>
+        <v>-2.627932258321524</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.093357309419484</v>
+        <v>2.086561210109889</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1828753830572007</v>
+        <v>-0.1998656313311873</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.028365307917926</v>
+        <v>3.018171158953534</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.954624783274201</v>
+        <v>-2.971615031548187</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.957653323583434</v>
+        <v>1.95085722427384</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.2907814350844189</v>
+        <v>-0.3077716833584055</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.965390800156211</v>
+        <v>2.955196651191819</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.312275133512549</v>
+        <v>-3.329265381786535</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.810699242144353</v>
+        <v>1.803903142834758</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.648431785322767</v>
+        <v>-0.6654220335967536</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.74690664866946</v>
+        <v>2.736712499705068</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.318936073734696</v>
+        <v>-3.335926322008683</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.809807792755753</v>
+        <v>1.803011693446159</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.648431785322767</v>
+        <v>-0.6654220335967536</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.74867957536972</v>
+        <v>2.738485426405328</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.750741866884484</v>
+        <v>-3.76773211515847</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.623418362963243</v>
+        <v>1.616622263653648</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.784849281764034</v>
+        <v>-0.8018395300380206</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.653161964972364</v>
+        <v>2.642967816007972</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.077174395752229</v>
+        <v>-4.094164644026215</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.481130126418236</v>
+        <v>1.474334027108641</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8673175322711821</v>
+        <v>-0.8843077805451687</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.591965789670166</v>
+        <v>2.581771640705774</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.078738546862532</v>
+        <v>-4.095728795136518</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.47908505763008</v>
+        <v>1.472288958320485</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8673175322711821</v>
+        <v>-0.8843077805451687</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.59054638132613</v>
+        <v>2.580352232361739</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.442364791762845</v>
+        <v>-4.459355040036831</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.340122119904196</v>
+        <v>1.333326020594602</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.965539169138308</v>
+        <v>-0.9825294174122945</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.538100959440097</v>
+        <v>2.527906810475705</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.439937727234127</v>
+        <v>-4.456927975508113</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.340347460721515</v>
+        <v>1.33355136141192</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.9658719509454596</v>
+        <v>-0.9828621992194462</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.537155805361637</v>
+        <v>2.526961656397245</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.848526504414805</v>
+        <v>-4.865516752688791</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.175673493864003</v>
+        <v>1.168877394554408</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.374460728126138</v>
+        <v>-1.391450976400125</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.290764083067989</v>
+        <v>2.280569934103597</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.261508988555899</v>
+        <v>-5.278499236829885</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.005665932679026</v>
+        <v>0.9988698333694312</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.374460728126138</v>
+        <v>-1.391450976400125</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.28594951553945</v>
+        <v>2.275755366575058</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.677900862842896</v>
+        <v>-5.694891111116882</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.8371032335731039</v>
+        <v>0.8303071342635095</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.374460728126138</v>
+        <v>-1.391450976400125</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.283943566148327</v>
+        <v>2.273749417183935</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.05457787337274</v>
+        <v>-6.071568121646727</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.6966911200298451</v>
+        <v>0.6898950207202508</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.374460728126138</v>
+        <v>-1.391450976400125</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.294202256817006</v>
+        <v>2.284008107852614</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.068292737697852</v>
+        <v>-6.085282985971838</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.6873047394454956</v>
+        <v>0.6805086401359013</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.374460728126138</v>
+        <v>-1.391450976400125</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.290301821962701</v>
+        <v>2.28010767299831</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.381117536942831</v>
+        <v>-6.398107785216817</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.5605797398025048</v>
+        <v>0.5537836404929104</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.374460728126138</v>
+        <v>-1.391450976400125</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.288706742017702</v>
+        <v>2.278512593053311</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969596</v>
+        <v>3.424633354969595</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.385930575408168</v>
+        <v>-6.402920823682154</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.5624335003455783</v>
+        <v>0.5556374010359839</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.376007362828924</v>
+        <v>-1.39299761110291</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.291557737125239</v>
+        <v>2.281363588160847</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.819279683518404</v>
+        <v>-6.836269931792391</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.3850675525670808</v>
+        <v>0.3782714532574865</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.376007362828924</v>
+        <v>-1.39299761110291</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.287531432590836</v>
+        <v>2.277337283626444</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.202281072261036</v>
+        <v>-7.219271320535022</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.2317648957484444</v>
+        <v>0.2249687964388496</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.376007362828924</v>
+        <v>-1.39299761110291</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.287429331269252</v>
+        <v>2.27723518230486</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.577266398432313</v>
+        <v>-7.594256646706299</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.08434228125136345</v>
+        <v>0.0775461819417691</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.750992689000201</v>
+        <v>-1.767982937274188</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.065009651537915</v>
+        <v>2.054815502573524</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.936796720936314</v>
+        <v>-7.9537869692103</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.05411954445218692</v>
+        <v>-0.06091564376178127</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.750992689000201</v>
+        <v>-1.767982937274188</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.070359954835966</v>
+        <v>2.060165805871573</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.263196749601327</v>
+        <v>-8.280186997875314</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1767635359610149</v>
+        <v>-0.1835596352706093</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.077392717665214</v>
+        <v>-2.094382965939201</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.882435957594135</v>
+        <v>1.872241808629744</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.256720602807768</v>
+        <v>-8.273710851081754</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.171131326621822</v>
+        <v>-0.1779274259314163</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.070916570871654</v>
+        <v>-2.087906819145641</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.88936339629204</v>
+        <v>1.879169247327648</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.253029677851357</v>
+        <v>-8.270019926125343</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1696549566392576</v>
+        <v>-0.1764510559488524</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.070916570871654</v>
+        <v>-2.087906819145641</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.88936339629204</v>
+        <v>1.879169247327648</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.457287853181221</v>
+        <v>-8.474278101455207</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2458450296525609</v>
+        <v>-0.2526411289621553</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.198555515485643</v>
+        <v>-2.21554576375963</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.818293226642289</v>
+        <v>1.808099077677897</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.617926879669586</v>
+        <v>-8.634917127943572</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3056180857634709</v>
+        <v>-0.3124141850730653</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.313288988488039</v>
+        <v>-2.330279236762026</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.753935697325288</v>
+        <v>1.743741548360896</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910627</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.544457048002137</v>
+        <v>-8.561447296276123</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2608584516030703</v>
+        <v>-0.2676545509126647</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.239819156820591</v>
+        <v>-2.256809405094577</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.813389297819178</v>
+        <v>1.803195148854786</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.71958146538868</v>
+        <v>-8.736571713662666</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3163529978101707</v>
+        <v>-0.323149097119765</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.414943574207134</v>
+        <v>-2.431933822481121</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.722869868134769</v>
+        <v>1.712675719170377</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.95403355940317</v>
+        <v>-8.971023807677156</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4173530003175627</v>
+        <v>-0.4241490996271571</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.414943574207134</v>
+        <v>-2.431933822481121</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.715650703233172</v>
+        <v>1.705456554268781</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.241837403940409</v>
+        <v>-9.258827652214395</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.539146728906434</v>
+        <v>-0.5459428282160288</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.702747418744373</v>
+        <v>-2.719737667018359</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.536296205736853</v>
+        <v>1.526102056772461</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.471661851104233</v>
+        <v>-9.48865209937822</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6299607179334079</v>
+        <v>-0.6367568172430023</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.865394955814533</v>
+        <v>-2.88238520408852</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.439823473333313</v>
+        <v>1.429629324368922</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.408592618797893</v>
+        <v>-9.42558286707188</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6020392963817573</v>
+        <v>-0.6088353956913517</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.893908518496767</v>
+        <v>-2.910898766770754</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.425409064353087</v>
+        <v>1.415214915388695</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792539</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.35657710482908</v>
+        <v>-9.373567353103066</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.577242755107831</v>
+        <v>-0.5840388544174253</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.893908518496767</v>
+        <v>-2.910898766770754</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.429399400039488</v>
+        <v>1.419205251075096</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.437869034383285</v>
+        <v>-9.454859282657271</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6112347538282545</v>
+        <v>-0.6180308531378489</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.893908518496767</v>
+        <v>-2.910898766770754</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.427924173140747</v>
+        <v>1.417730024176355</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410714</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.240599628655287</v>
+        <v>-9.257589876929273</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5172735813721832</v>
+        <v>-0.5240696806817779</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.696639112768769</v>
+        <v>-2.713629361042756</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.561339226742418</v>
+        <v>1.551145077778026</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240573</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.041447521418188</v>
+        <v>-9.058437769692175</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4506638721240268</v>
+        <v>-0.4574599714336212</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.531316586818956</v>
+        <v>-2.548306835092943</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.647481608665623</v>
+        <v>1.637287459701231</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085276</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.815602368698777</v>
+        <v>-8.832592616972764</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3507467380000535</v>
+        <v>-0.3575428373096483</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.489389911231792</v>
+        <v>-2.506380159505779</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.68221668705413</v>
+        <v>1.672022538089738</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.529327556376082</v>
+        <v>-8.546317804650069</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.2350976685149164</v>
+        <v>-0.2418937678245117</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.489389911231792</v>
+        <v>-2.506380159505779</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.683355831610188</v>
+        <v>1.673161682645796</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.302531729302748</v>
+        <v>-8.319521977576736</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.1417455635234752</v>
+        <v>-0.1485416628330705</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.421275966610248</v>
+        <v>-2.438266214884234</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.726857972545223</v>
+        <v>1.716663823580831</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.018622998373999</v>
+        <v>-8.035613246647987</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.02244836691333951</v>
+        <v>-0.02924446622293431</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.421275966610248</v>
+        <v>-2.438266214884234</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.732591676783859</v>
+        <v>1.722397527819467</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-7.771635748181047</v>
+        <v>-7.788625996455035</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.06660927076997636</v>
+        <v>0.05981317146038112</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.174288716417296</v>
+        <v>-2.191278964691282</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.871046764505765</v>
+        <v>1.860852615541373</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-7.507798880976978</v>
+        <v>-7.524789129250966</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.1622605363386964</v>
+        <v>0.1554644370291012</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.174288716417296</v>
+        <v>-2.191278964691282</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.861163283192858</v>
+        <v>1.850969134228466</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.240557080108581</v>
+        <v>-7.257547328382569</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.2673226961866813</v>
+        <v>0.2605265968770865</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.174288716417296</v>
+        <v>-2.191278964691282</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.859328722693484</v>
+        <v>1.849134573729092</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.964747916708097</v>
+        <v>-6.981738164982085</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.3773460465734142</v>
+        <v>0.370549947263819</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.085269408138562</v>
+        <v>-2.102259656412549</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.912439992687263</v>
+        <v>1.902245843722871</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.695680328941117</v>
+        <v>-6.712670577215105</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.4856415878256999</v>
+        <v>0.4788454885161046</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.816201820371583</v>
+        <v>-1.83319206864557</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.074549051492944</v>
+        <v>2.064354902528553</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.431620390618321</v>
+        <v>-6.448610638892309</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.5780052469930661</v>
+        <v>0.5712091476834709</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.552141882048787</v>
+        <v>-1.569132130322773</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.21972469832487</v>
+        <v>2.209530549360478</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309728</v>
+        <v>3.833249172309726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-5.724540767113483</v>
+        <v>-5.741531015387471</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.8580500627347005</v>
+        <v>0.8512539634251053</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.552141882048787</v>
+        <v>-1.569132130322773</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.216937664664569</v>
+        <v>2.206743515700177</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-5.474899737127531</v>
+        <v>-5.491889985401519</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.9582500986169227</v>
+        <v>0.9514539993073274</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.302500852062835</v>
+        <v>-1.319491100336822</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.367065906543981</v>
+        <v>2.35687175757959</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.220357837786455</v>
+        <v>-5.237348086060443</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.05943367957411</v>
+        <v>1.052637580264515</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.04795895272176</v>
+        <v>-1.064949200995746</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.519157867369384</v>
+        <v>2.508963718404992</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-4.986876615556857</v>
+        <v>-5.003866863830845</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.160750597303802</v>
+        <v>1.153954497994206</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8144777304921611</v>
+        <v>-0.8314679787661476</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.667171029544996</v>
+        <v>2.656976880580603</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.807168085412984</v>
+        <v>-4.824158333686972</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.229741799048392</v>
+        <v>1.222945699738796</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.757306226329465</v>
+        <v>-0.7742964746034515</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.698581721729654</v>
+        <v>2.688387572765262</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.674892611782098</v>
+        <v>-4.691882860056086</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.278019475247773</v>
+        <v>1.271223375938178</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6250307526985783</v>
+        <v>-0.6420210009725649</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.773314492655213</v>
+        <v>2.763120343690821</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.784715218575952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.484292937108945</v>
+        <v>-4.501283185382933</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.357074405804671</v>
+        <v>1.350278306495076</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4344310780254255</v>
+        <v>-0.451421326299412</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.890489358146741</v>
+        <v>2.880295209182349</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.235293138425364</v>
+        <v>-4.252283386699352</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.469580666501762</v>
+        <v>1.462784567192167</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1854312793418448</v>
+        <v>-0.2024215276158313</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.052795578580549</v>
+        <v>3.042601429616156</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-4.043914063564424</v>
+        <v>-4.060904311838412</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.418156366846919</v>
+        <v>1.411360267537324</v>
       </c>
       <c r="F1908" t="n">
-        <v>0.0059477955190953</v>
+        <v>-0.01104245275489124</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.039647093897894</v>
+        <v>3.029452944933502</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-3.764886767908797</v>
+        <v>-3.781877016182785</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.578311626986257</v>
+        <v>1.571515527676661</v>
       </c>
       <c r="F1909" t="n">
-        <v>0.0059477955190953</v>
+        <v>-0.01104245275489124</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.08819143577498</v>
+        <v>3.077997286810588</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-3.488148593237984</v>
+        <v>-3.505138841511972</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.692385908840576</v>
+        <v>1.685589809530981</v>
       </c>
       <c r="F1910" t="n">
-        <v>0.1877644566290211</v>
+        <v>0.1707742083550345</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.20066044442693</v>
+        <v>3.190466295462538</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-3.361256186802914</v>
+        <v>-3.378246435076902</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.734428885161126</v>
+        <v>1.727632785851531</v>
       </c>
       <c r="F1911" t="n">
-        <v>0.314656863064091</v>
+        <v>0.2976666147901045</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.268081902034494</v>
+        <v>3.257887753070102</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-3.173668678892988</v>
+        <v>-3.190658927166976</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.802503276230004</v>
+        <v>1.795707176920408</v>
       </c>
       <c r="F1912" t="n">
-        <v>0.314656863064091</v>
+        <v>0.2976666147901045</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.261121289939401</v>
+        <v>3.250927140975009</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-2.93152028543913</v>
+        <v>-2.948510533713117</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.91382498799269</v>
+        <v>1.907028888683095</v>
       </c>
       <c r="F1913" t="n">
-        <v>0.314656863064091</v>
+        <v>0.2976666147901045</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.275583644320544</v>
+        <v>3.265389495356152</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192815</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-2.868290913670781</v>
+        <v>-2.885281161944769</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.933648857159224</v>
+        <v>1.92685275784963</v>
       </c>
       <c r="F1914" t="n">
-        <v>0.314656863064091</v>
+        <v>0.2976666147901045</v>
       </c>
       <c r="G1914" t="n">
-        <v>3.270115764779739</v>
+        <v>3.259921615815347</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262046</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-2.87224532576084</v>
+        <v>-2.698793469567763</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.929565186333778</v>
+        <v>1.998945928811009</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.3107024509740327</v>
+        <v>0.4841543071671107</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.265241211536281</v>
+        <v>3.369312325252128</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,19 +45613,19 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.54896982266024</v>
+        <v>3.548969822660238</v>
       </c>
       <c r="C1916" t="n">
         <v>2.895626040749816</v>
       </c>
       <c r="D1916" t="n">
-        <v>-2.87224532576084</v>
+        <v>-2.698793469567763</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.929565186333778</v>
+        <v>1.998945928811009</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.3107024509740327</v>
+        <v>0.4841543071671107</v>
       </c>
       <c r="G1916" t="n">
         <v>2.888689837736183</v>

--- a/tame_output/ON/bt/strategyON_20240327.xlsx
+++ b/tame_output/ON/bt/strategyON_20240327.xlsx
@@ -45616,7 +45616,7 @@
         <v>3.548969822660238</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.895626040749816</v>
+        <v>2.895626040749815</v>
       </c>
       <c r="D1916" t="n">
         <v>-2.698793469567763</v>

--- a/tame_output/ON/bt/strategyON_20240327.xlsx
+++ b/tame_output/ON/bt/strategyON_20240327.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>51.9%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>124.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-45.5%</t>
+          <t>-45.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-65.0%</t>
+          <t>-64.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>908.0%</t>
+          <t>913.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-431.5%</t>
+          <t>-431.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-50.6%</t>
+          <t>-50.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-27.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-176.3%</t>
+          <t>-194.7%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.2%</t>
+          <t>-155.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-175.6%</t>
+          <t>-176.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-27.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-157.2%</t>
+          <t>-127.8%</t>
         </is>
       </c>
     </row>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153008</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537427</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.48865209937822</v>
+        <v>-9.493359223462418</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6367568172430023</v>
+        <v>-0.6386396668766818</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.88238520408852</v>
+        <v>-2.8914104528226</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.429629324368922</v>
+        <v>1.424214175128473</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.42558286707188</v>
+        <v>-9.430289991156078</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6088353956913517</v>
+        <v>-0.6107182453250313</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.910898766770754</v>
+        <v>-2.919924015504835</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.415214915388695</v>
+        <v>1.409799766148247</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792539</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.373567353103066</v>
+        <v>-9.378274477187265</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5840388544174253</v>
+        <v>-0.5859217040511049</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.910898766770754</v>
+        <v>-2.919924015504835</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.419205251075096</v>
+        <v>1.413790101834648</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.454859282657271</v>
+        <v>-9.45956640674147</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6180308531378489</v>
+        <v>-0.6199137027715285</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.910898766770754</v>
+        <v>-2.919924015504835</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.417730024176355</v>
+        <v>1.412314874935906</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.257589876929273</v>
+        <v>-9.262297001013472</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5240696806817779</v>
+        <v>-0.5259525303154571</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.713629361042756</v>
+        <v>-2.722654609776836</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.551145077778026</v>
+        <v>1.545729928537577</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.058437769692175</v>
+        <v>-9.063144893776373</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4574599714336212</v>
+        <v>-0.4593428210673007</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.548306835092943</v>
+        <v>-2.557332083827023</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.637287459701231</v>
+        <v>1.631872310460782</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.832592616972764</v>
+        <v>-8.837299741056963</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3575428373096483</v>
+        <v>-0.3594256869433279</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.506380159505779</v>
+        <v>-2.51540540823986</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.672022538089738</v>
+        <v>1.666607388849289</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.546317804650069</v>
+        <v>-8.551024928734268</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.2418937678245117</v>
+        <v>-0.2437766174581912</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.506380159505779</v>
+        <v>-2.51540540823986</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.673161682645796</v>
+        <v>1.667746533405348</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.319521977576736</v>
+        <v>-8.324229101660935</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.1485416628330705</v>
+        <v>-0.15042451246675</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.438266214884234</v>
+        <v>-2.447291463618315</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.716663823580831</v>
+        <v>1.711248674340382</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.035613246647987</v>
+        <v>-8.040320370732186</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.02924446622293431</v>
+        <v>-0.03112731585661388</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.438266214884234</v>
+        <v>-2.447291463618315</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.722397527819467</v>
+        <v>1.716982378579019</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-7.788625996455035</v>
+        <v>-7.793333120539233</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.05981317146038112</v>
+        <v>0.05793032182670199</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.191278964691282</v>
+        <v>-2.200304213425363</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.860852615541373</v>
+        <v>1.855437466300925</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-7.524789129250966</v>
+        <v>-7.529496253335164</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.1554644370291012</v>
+        <v>0.1535815873954216</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.191278964691282</v>
+        <v>-2.200304213425363</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.850969134228466</v>
+        <v>1.845553984988017</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.257547328382569</v>
+        <v>-7.262254452466768</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.2605265968770865</v>
+        <v>0.2586437472434069</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.191278964691282</v>
+        <v>-2.200304213425363</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.849134573729092</v>
+        <v>1.843719424488644</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.981738164982085</v>
+        <v>-6.986445289066284</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.370549947263819</v>
+        <v>0.3686670976301394</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.102259656412549</v>
+        <v>-2.11128490514663</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.902245843722871</v>
+        <v>1.896830694482423</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.712670577215105</v>
+        <v>-6.717377701299304</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.4788454885161046</v>
+        <v>0.4769626388824251</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.83319206864557</v>
+        <v>-1.84221731737965</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.064354902528553</v>
+        <v>2.058939753288104</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.448610638892309</v>
+        <v>-6.453317762976508</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.5712091476834709</v>
+        <v>0.5693262980497913</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.569132130322773</v>
+        <v>-1.578157379056854</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.209530549360478</v>
+        <v>2.204115400120029</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-5.741531015387471</v>
+        <v>-5.74623813947167</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.8512539634251053</v>
+        <v>0.8493711137914257</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.569132130322773</v>
+        <v>-1.578157379056854</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.206743515700177</v>
+        <v>2.201328366459729</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-5.491889985401519</v>
+        <v>-5.496597109485718</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.9514539993073274</v>
+        <v>0.9495711496736479</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.319491100336822</v>
+        <v>-1.328516349070902</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.35687175757959</v>
+        <v>2.351456608339141</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.237348086060443</v>
+        <v>-5.242055210144642</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.052637580264515</v>
+        <v>1.050754730630835</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.064949200995746</v>
+        <v>-1.073974449729827</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.508963718404992</v>
+        <v>2.503548569164543</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.003866863830845</v>
+        <v>-5.008573987915043</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.153954497994206</v>
+        <v>1.152071648360527</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8314679787661476</v>
+        <v>-0.8404932275002284</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.656976880580603</v>
+        <v>2.651561731340155</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.824158333686972</v>
+        <v>-4.828865457771171</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.222945699738796</v>
+        <v>1.221062850105117</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7742964746034515</v>
+        <v>-0.7833217233375322</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.688387572765262</v>
+        <v>2.682972423524813</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.691882860056086</v>
+        <v>-4.696589984140284</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.271223375938178</v>
+        <v>1.269340526304499</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6420210009725649</v>
+        <v>-0.6510462497066456</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.763120343690821</v>
+        <v>2.757705194450372</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575952</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.501283185382933</v>
+        <v>-4.505990309467132</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.350278306495076</v>
+        <v>1.348395456861396</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.451421326299412</v>
+        <v>-0.4604465750334927</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.880295209182349</v>
+        <v>2.874880059941901</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.252283386699352</v>
+        <v>-4.256990510783551</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.462784567192167</v>
+        <v>1.460901717558488</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2024215276158313</v>
+        <v>-0.211446776349912</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.042601429616156</v>
+        <v>3.037186280375708</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-4.060904311838412</v>
+        <v>-4.065611435922611</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.411360267537324</v>
+        <v>1.409477417903645</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.01104245275489124</v>
+        <v>-0.02006770148897197</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.029452944933502</v>
+        <v>3.024037795693054</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-3.781877016182785</v>
+        <v>-3.786584140266983</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.571515527676661</v>
+        <v>1.569632678042982</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.01104245275489124</v>
+        <v>-0.02006770148897197</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.077997286810588</v>
+        <v>3.07258213757014</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-3.505138841511972</v>
+        <v>-3.509845965596171</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.685589809530981</v>
+        <v>1.683706959897302</v>
       </c>
       <c r="F1910" t="n">
-        <v>0.1707742083550345</v>
+        <v>0.1617489596209538</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.190466295462538</v>
+        <v>3.18505114622209</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-3.378246435076902</v>
+        <v>-3.382953559161101</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.727632785851531</v>
+        <v>1.725749936217851</v>
       </c>
       <c r="F1911" t="n">
-        <v>0.2976666147901045</v>
+        <v>0.2886413660560238</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.257887753070102</v>
+        <v>3.252472603829653</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-3.190658927166976</v>
+        <v>-3.195366051251174</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.795707176920408</v>
+        <v>1.793824327286729</v>
       </c>
       <c r="F1912" t="n">
-        <v>0.2976666147901045</v>
+        <v>0.2886413660560238</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.250927140975009</v>
+        <v>3.24551199173456</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-2.948510533713117</v>
+        <v>-2.953217657797316</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.907028888683095</v>
+        <v>1.905146039049415</v>
       </c>
       <c r="F1913" t="n">
-        <v>0.2976666147901045</v>
+        <v>0.2886413660560238</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.265389495356152</v>
+        <v>3.259974346115703</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-2.885281161944769</v>
+        <v>-2.889988286028968</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.92685275784963</v>
+        <v>1.924969908215949</v>
       </c>
       <c r="F1914" t="n">
-        <v>0.2976666147901045</v>
+        <v>0.2886413660560238</v>
       </c>
       <c r="G1914" t="n">
-        <v>3.259921615815347</v>
+        <v>3.254506466574898</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-2.698793469567763</v>
+        <v>-2.703500593651961</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.998945928811009</v>
+        <v>1.997063079177329</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.4841543071671107</v>
+        <v>0.47512905843303</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.369312325252128</v>
+        <v>3.363897176011679</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.548969822660238</v>
+        <v>3.799713131178736</v>
       </c>
       <c r="C1916" t="n">
         <v>2.895626040749815</v>
       </c>
       <c r="D1916" t="n">
-        <v>-2.698793469567763</v>
+        <v>-2.700609737712791</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.998945928811009</v>
+        <v>1.815025721350952</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.4841543071671107</v>
+        <v>0.4780199143722005</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.888689837736183</v>
+        <v>3.182437989373136</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240327.xlsx
+++ b/tame_output/ON/bt/strategyON_20240327.xlsx
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,25 +801,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-27.1%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-22.1%</t>
+          <t>-3.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-69.5%</t>
+          <t>-67.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>107.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.5%</t>
+          <t>122.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-571.0%</t>
+          <t>-539.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-45.6%</t>
+          <t>-44.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-64.6%</t>
+          <t>-61.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>913.1%</t>
+          <t>502.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-431.6%</t>
+          <t>-402.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-228.8%</t>
+          <t>-216.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.4%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-50.5%</t>
+          <t>-63.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-146.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-194.7%</t>
+          <t>-164.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-312.4%</t>
+          <t>-281.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-30.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.0%</t>
+          <t>-145.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-176.2%</t>
+          <t>-145.7%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-187.8%</t>
+          <t>-169.2%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.7%</t>
+          <t>-26.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-127.8%</t>
+          <t>-90.4%</t>
         </is>
       </c>
     </row>
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.1102648519860253</v>
+        <v>0.4214543533367376</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.178584594900222</v>
+        <v>3.303060395440507</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.506376488380516</v>
+        <v>1.817565989731229</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.03866097144787</v>
+        <v>4.225374672258297</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.04449746193661325</v>
+        <v>0.3556869632873255</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.153295248010928</v>
+        <v>3.277771048551212</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.506376488380516</v>
+        <v>1.817565989731229</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.03967858057834</v>
+        <v>4.226392281388767</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.03096197815990365</v>
+        <v>0.3421514795106159</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.138509086487999</v>
+        <v>3.262984887028284</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.506376488380516</v>
+        <v>1.817565989731229</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.030306612566095</v>
+        <v>4.217020313376523</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.05080992226784803</v>
+        <v>0.2603795790828642</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.095883052272137</v>
+        <v>3.220358852812422</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.533412061786653</v>
+        <v>1.844601563137365</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.036610682565016</v>
+        <v>4.223324383375443</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.1180190301397257</v>
+        <v>0.1931704712109866</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.073764725957088</v>
+        <v>3.198240526497373</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.533412061786653</v>
+        <v>1.844601563137365</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.041375999398718</v>
+        <v>4.228089700209145</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.1140275773445355</v>
+        <v>0.1971619240061768</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.073186103194405</v>
+        <v>3.19766190373469</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.537403514581843</v>
+        <v>1.848593015932555</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.041595667195073</v>
+        <v>4.228309368005499</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.5121760082977962</v>
+        <v>-0.2009865069470839</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.911853622318163</v>
+        <v>3.036329422858449</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.139255083628583</v>
+        <v>1.450444584979295</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.800633500128179</v>
+        <v>3.987347200938607</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.7337979418559137</v>
+        <v>-0.4226084405052014</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.823071065493838</v>
+        <v>2.947546866034124</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.101728949941214</v>
+        <v>1.412918451291926</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.77798403651468</v>
+        <v>3.964697737325107</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.941802000208991</v>
+        <v>-0.6306124988582786</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.744761586706533</v>
+        <v>2.869237387246818</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.101728949941214</v>
+        <v>1.412918451291926</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.782876181068605</v>
+        <v>3.969589881879032</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.212201962917876</v>
+        <v>-0.901012461567164</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.631683057960967</v>
+        <v>2.756158858501252</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.8313289872323282</v>
+        <v>1.14251848858304</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.615717659781262</v>
+        <v>3.802431360591689</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.551360340506398</v>
+        <v>-1.240170839155686</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.489104006232007</v>
+        <v>2.613579806772292</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.4921706096438061</v>
+        <v>0.8033601109945183</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.405306932534597</v>
+        <v>3.592020633345025</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.879377562233877</v>
+        <v>-1.568188060883165</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.378235407279784</v>
+        <v>2.502711207820068</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.1641533879163269</v>
+        <v>0.4753428892670392</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.228834889236878</v>
+        <v>3.415548590047305</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.876040815724906</v>
+        <v>-1.564851314374194</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.387668856291941</v>
+        <v>2.512144656832226</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.1668454203353583</v>
+        <v>0.4780349216860705</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.238548859096866</v>
+        <v>3.425262559907293</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.242751867391451</v>
+        <v>-1.931562366040739</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.242090827669055</v>
+        <v>2.366566628209339</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1998656313311873</v>
+        <v>0.1113238700195249</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.01962862014067</v>
+        <v>3.206342320951098</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.627932258321524</v>
+        <v>-2.316742756970812</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.086561210109889</v>
+        <v>2.211037010650174</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1998656313311873</v>
+        <v>0.1113238700195249</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.018171158953534</v>
+        <v>3.204884859763961</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.971615031548187</v>
+        <v>-2.660425530197474</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.95085722427384</v>
+        <v>2.075333024814125</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.3077716833584055</v>
+        <v>0.003417817992306726</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.955196651191819</v>
+        <v>3.141910352002246</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.329265381786535</v>
+        <v>-3.018075880435823</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.803903142834758</v>
+        <v>1.928378943375043</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6654220335967536</v>
+        <v>-0.3542325322460414</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.736712499705068</v>
+        <v>2.923426200515495</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.335926322008683</v>
+        <v>-3.02473682065797</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.803011693446159</v>
+        <v>1.927487493986444</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6654220335967536</v>
+        <v>-0.3542325322460414</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.738485426405328</v>
+        <v>2.925199127215755</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.76773211515847</v>
+        <v>-3.456542613807758</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.616622263653648</v>
+        <v>1.741098064193933</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8018395300380206</v>
+        <v>-0.4906500286873084</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.642967816007972</v>
+        <v>2.829681516818399</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.094164644026215</v>
+        <v>-3.782975142675502</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.474334027108641</v>
+        <v>1.598809827648927</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8843077805451687</v>
+        <v>-0.5731182791944566</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.581771640705774</v>
+        <v>2.768485341516201</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.095728795136518</v>
+        <v>-3.784539293785805</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.472288958320485</v>
+        <v>1.596764758860771</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8843077805451687</v>
+        <v>-0.5731182791944566</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.580352232361739</v>
+        <v>2.767065933172166</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.459355040036831</v>
+        <v>-4.148165538686118</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.333326020594602</v>
+        <v>1.457801821134887</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9825294174122945</v>
+        <v>-0.6713399160615824</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.527906810475705</v>
+        <v>2.714620511286132</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.456927975508113</v>
+        <v>-4.145738474157399</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.33355136141192</v>
+        <v>1.458027161952206</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.9828621992194462</v>
+        <v>-0.671672697868734</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.526961656397245</v>
+        <v>2.713675357207673</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.865516752688791</v>
+        <v>-4.554327251338078</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.168877394554408</v>
+        <v>1.293353195094693</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.391450976400125</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.280569934103597</v>
+        <v>2.467283634914025</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.278499236829885</v>
+        <v>-4.967309735479172</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.9988698333694312</v>
+        <v>1.123345633909716</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.391450976400125</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.275755366575058</v>
+        <v>2.462469067385485</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.694891111116882</v>
+        <v>-5.383701609766169</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.8303071342635095</v>
+        <v>0.9547829348037946</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.391450976400125</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.273749417183935</v>
+        <v>2.460463117994363</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.071568121646727</v>
+        <v>-5.760378620296014</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.6898950207202508</v>
+        <v>0.8143708212605358</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.391450976400125</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.284008107852614</v>
+        <v>2.470721808663042</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.085282985971838</v>
+        <v>-5.774093484621125</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.6805086401359013</v>
+        <v>0.8049844406761864</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.391450976400125</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.28010767299831</v>
+        <v>2.466821373808737</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.398107785216817</v>
+        <v>-6.086918283866105</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.5537836404929104</v>
+        <v>0.6782594410331955</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.391450976400125</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.278512593053311</v>
+        <v>2.465226293863738</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.402920823682154</v>
+        <v>-6.091731322331442</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.5556374010359839</v>
+        <v>0.680113201576269</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.39299761110291</v>
+        <v>-1.081808109752198</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.281363588160847</v>
+        <v>2.468077288971275</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.836269931792391</v>
+        <v>-6.525080430441678</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.3782714532574865</v>
+        <v>0.5027472537977715</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.39299761110291</v>
+        <v>-1.081808109752198</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.277337283626444</v>
+        <v>2.464050984436871</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.219271320535022</v>
+        <v>-6.908081819184309</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.2249687964388496</v>
+        <v>0.3494445969791347</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.39299761110291</v>
+        <v>-1.081808109752198</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.27723518230486</v>
+        <v>2.463948883115287</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.594256646706299</v>
+        <v>-7.283067145355586</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.0775461819417691</v>
+        <v>0.2020219824820542</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.767982937274188</v>
+        <v>-1.456793435923476</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.054815502573524</v>
+        <v>2.241529203383951</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.9537869692103</v>
+        <v>-7.642597467859588</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.06091564376178127</v>
+        <v>0.0635601567785038</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.767982937274188</v>
+        <v>-1.456793435923476</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.060165805871573</v>
+        <v>2.246879506682001</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.280186997875314</v>
+        <v>-7.968997496524601</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1835596352706093</v>
+        <v>-0.05908383473032419</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.094382965939201</v>
+        <v>-1.783193464588488</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.872241808629744</v>
+        <v>2.058955509440171</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.273710851081754</v>
+        <v>-7.962521349731041</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1779274259314163</v>
+        <v>-0.05345162539113124</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.087906819145641</v>
+        <v>-1.776717317794929</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.879169247327648</v>
+        <v>2.065882948138076</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.270019926125343</v>
+        <v>-7.95883042477463</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1764510559488524</v>
+        <v>-0.05197525540856685</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.087906819145641</v>
+        <v>-1.776717317794929</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.879169247327648</v>
+        <v>2.065882948138076</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.474278101455207</v>
+        <v>-8.163088600104492</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2526411289621553</v>
+        <v>-0.1281653284218693</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.21554576375963</v>
+        <v>-1.904356262408918</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.808099077677897</v>
+        <v>1.994812778488325</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.634917127943572</v>
+        <v>-8.323727626592857</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3124141850730653</v>
+        <v>-0.1879383845327793</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.330279236762026</v>
+        <v>-2.019089735411313</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.743741548360896</v>
+        <v>1.930455249171323</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.561447296276123</v>
+        <v>-8.250257794925409</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2676545509126647</v>
+        <v>-0.1431787503723787</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.256809405094577</v>
+        <v>-1.945619903743865</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.803195148854786</v>
+        <v>1.989908849665214</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.736571713662666</v>
+        <v>-8.425382212311952</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.323149097119765</v>
+        <v>-0.1986732965794795</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.431933822481121</v>
+        <v>-2.120744321130409</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.712675719170377</v>
+        <v>1.899389419980804</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.971023807677156</v>
+        <v>-8.659834306326442</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4241490996271571</v>
+        <v>-0.2996732990868711</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.431933822481121</v>
+        <v>-2.120744321130409</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.705456554268781</v>
+        <v>1.892170255079208</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.258827652214395</v>
+        <v>-8.94763815086368</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5459428282160288</v>
+        <v>-0.4214670276757428</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.719737667018359</v>
+        <v>-2.408548165667647</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.526102056772461</v>
+        <v>1.712815757582889</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.493359223462418</v>
+        <v>-9.204494196622758</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6386396668766818</v>
+        <v>-0.5230936561408175</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.8914104528226</v>
+        <v>-2.586651052271671</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.424214175128473</v>
+        <v>1.60706981545903</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.430289991156078</v>
+        <v>-9.141424964316418</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6107182453250313</v>
+        <v>-0.4951722345891669</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.919924015504835</v>
+        <v>-2.615164614953906</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.409799766148247</v>
+        <v>1.592655406478805</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.378274477187265</v>
+        <v>-9.089409450347604</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5859217040511049</v>
+        <v>-0.4703756933152405</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.919924015504835</v>
+        <v>-2.615164614953906</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.413790101834648</v>
+        <v>1.596645742165205</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.45956640674147</v>
+        <v>-9.170701379901809</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6199137027715285</v>
+        <v>-0.5043676920356641</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.919924015504835</v>
+        <v>-2.615164614953906</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.412314874935906</v>
+        <v>1.595170515266464</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.262297001013472</v>
+        <v>-8.973431974173812</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5259525303154571</v>
+        <v>-0.4104065195795932</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.722654609776836</v>
+        <v>-2.417895209225907</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.545729928537577</v>
+        <v>1.728585568868135</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.063144893776373</v>
+        <v>-8.774279866936713</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4593428210673007</v>
+        <v>-0.3437968103314364</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.557332083827023</v>
+        <v>-2.252572683276094</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.631872310460782</v>
+        <v>1.81472795079134</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.837299741056963</v>
+        <v>-8.548434714217301</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3594256869433279</v>
+        <v>-0.2438796762074631</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.51540540823986</v>
+        <v>-2.21064600768893</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.666607388849289</v>
+        <v>1.849463029179847</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.551024928734268</v>
+        <v>-8.262159901894606</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.2437766174581912</v>
+        <v>-0.128230606722326</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.51540540823986</v>
+        <v>-2.21064600768893</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.667746533405348</v>
+        <v>1.850602173735906</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.324229101660935</v>
+        <v>-8.035364074821272</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.15042451246675</v>
+        <v>-0.03487850173088525</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.447291463618315</v>
+        <v>-2.142532063067386</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.711248674340382</v>
+        <v>1.89410431467094</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.040320370732186</v>
+        <v>-7.751455343892523</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.03112731585661388</v>
+        <v>0.08441869487925091</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.447291463618315</v>
+        <v>-2.142532063067386</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.716982378579019</v>
+        <v>1.899838018909576</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-7.793333120539233</v>
+        <v>-7.504468093699571</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.05793032182670199</v>
+        <v>0.1734763325625668</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.200304213425363</v>
+        <v>-1.895544812874434</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.855437466300925</v>
+        <v>2.038293106631483</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-7.529496253335164</v>
+        <v>-7.240631226495502</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.1535815873954216</v>
+        <v>0.2691275981312868</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.200304213425363</v>
+        <v>-1.895544812874434</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.845553984988017</v>
+        <v>2.028409625318575</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-7.262254452466768</v>
+        <v>-6.973389425627105</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.2586437472434069</v>
+        <v>0.3741897579792717</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.200304213425363</v>
+        <v>-1.895544812874434</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.843719424488644</v>
+        <v>2.026575064819201</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.986445289066284</v>
+        <v>-6.697580262226621</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.3686670976301394</v>
+        <v>0.4842131083660046</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.11128490514663</v>
+        <v>-1.8065255045957</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.896830694482423</v>
+        <v>2.079686334812981</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.717377701299304</v>
+        <v>-6.428512674459641</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.4769626388824251</v>
+        <v>0.5925086496182899</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.84221731737965</v>
+        <v>-1.537457916828721</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.058939753288104</v>
+        <v>2.241795393618661</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.453317762976508</v>
+        <v>-6.164452736136846</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.5693262980497913</v>
+        <v>0.6848723087856561</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.578157379056854</v>
+        <v>-1.273397978505925</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.204115400120029</v>
+        <v>2.386971040450587</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-5.74623813947167</v>
+        <v>-5.457373112632007</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.8493711137914257</v>
+        <v>0.9649171245272909</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.578157379056854</v>
+        <v>-1.273397978505925</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.201328366459729</v>
+        <v>2.384184006790286</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-5.496597109485718</v>
+        <v>-5.207732082646055</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.9495711496736479</v>
+        <v>1.065117160409513</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.328516349070902</v>
+        <v>-1.023756948519973</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.351456608339141</v>
+        <v>2.534312248669699</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-5.242055210144642</v>
+        <v>-4.953190183304979</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.050754730630835</v>
+        <v>1.1663007413667</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.073974449729827</v>
+        <v>-0.7692150491788978</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.503548569164543</v>
+        <v>2.686404209495101</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.008573987915043</v>
+        <v>-4.719708961075381</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.152071648360527</v>
+        <v>1.267617659096392</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8404932275002284</v>
+        <v>-0.5357338269492993</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.651561731340155</v>
+        <v>2.834417371670712</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.828865457771171</v>
+        <v>-4.540000430931508</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.221062850105117</v>
+        <v>1.336608860840982</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7833217233375322</v>
+        <v>-0.4785623227866032</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.682972423524813</v>
+        <v>2.865828063855371</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.696589984140284</v>
+        <v>-4.407724957300622</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.269340526304499</v>
+        <v>1.384886537040364</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6510462497066456</v>
+        <v>-0.3462868491557165</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.757705194450372</v>
+        <v>2.94056083478093</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.505990309467132</v>
+        <v>-4.217125282627469</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.348395456861396</v>
+        <v>1.463941467597261</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4604465750334927</v>
+        <v>-0.1556871744825636</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.874880059941901</v>
+        <v>3.057735700272458</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-4.256990510783551</v>
+        <v>-3.968125483943889</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.460901717558488</v>
+        <v>1.576447728294352</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.211446776349912</v>
+        <v>0.09331262420101705</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.037186280375708</v>
+        <v>3.220041920706266</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-4.065611435922611</v>
+        <v>-3.776746409082949</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.409477417903645</v>
+        <v>1.52502342863951</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.02006770148897197</v>
+        <v>0.2846916990619571</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.024037795693054</v>
+        <v>3.206893436023611</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-3.786584140266983</v>
+        <v>-3.497719113427322</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.569632678042982</v>
+        <v>1.685178688778847</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.02006770148897197</v>
+        <v>0.2846916990619571</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.07258213757014</v>
+        <v>3.255437777900697</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-3.509845965596171</v>
+        <v>-3.220980938756509</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.683706959897302</v>
+        <v>1.799252970633166</v>
       </c>
       <c r="F1910" t="n">
-        <v>0.1617489596209538</v>
+        <v>0.4665083601718829</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.18505114622209</v>
+        <v>3.367906786552648</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-3.382953559161101</v>
+        <v>-3.09408853232144</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.725749936217851</v>
+        <v>1.841295946953716</v>
       </c>
       <c r="F1911" t="n">
-        <v>0.2886413660560238</v>
+        <v>0.5934007666069528</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.252472603829653</v>
+        <v>3.435328244160211</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-3.195366051251174</v>
+        <v>-2.906501024411513</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.793824327286729</v>
+        <v>1.909370338022594</v>
       </c>
       <c r="F1912" t="n">
-        <v>0.2886413660560238</v>
+        <v>0.5934007666069528</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.24551199173456</v>
+        <v>3.428367632065118</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-2.953217657797316</v>
+        <v>-2.664352630957655</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.905146039049415</v>
+        <v>2.02069204978528</v>
       </c>
       <c r="F1913" t="n">
-        <v>0.2886413660560238</v>
+        <v>0.5934007666069528</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.259974346115703</v>
+        <v>3.442829986446261</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-2.889988286028968</v>
+        <v>-2.601123259189306</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.924969908215949</v>
+        <v>2.040515918951814</v>
       </c>
       <c r="F1914" t="n">
-        <v>0.2886413660560238</v>
+        <v>0.5934007666069528</v>
       </c>
       <c r="G1914" t="n">
-        <v>3.254506466574898</v>
+        <v>3.437362106905456</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-2.703500593651961</v>
+        <v>-2.4146355668123</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.997063079177329</v>
+        <v>2.112609089913194</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.47512905843303</v>
+        <v>0.7798884589839591</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.363897176011679</v>
+        <v>3.546752816342237</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.799713131178736</v>
+        <v>3.799713131178735</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.895626040749815</v>
+        <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-2.700609737712791</v>
+        <v>-2.411791197361112</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.815025721350952</v>
+        <v>2.121447815930995</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.4780199143722005</v>
+        <v>0.7827328284351465</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.182437989373136</v>
+        <v>3.556160416250274</v>
       </c>
     </row>
   </sheetData>
